--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="89">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Auteur du document (humain ou système)</t>
+    <t>1.2- Auteur du document (humain ou système)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,10 +260,26 @@
     <t>Horodatage de la participation de l’auteur.</t>
   </si>
   <si>
+    <t>AuteurDocument.roleFonctionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Rôle fonctionnel de l’auteur.</t>
+  </si>
+  <si>
+    <t>AuteurDocument.precisionRoleFonctionnel</t>
+  </si>
+  <si>
+    <t>Précision sur le rôle fonctionnel.</t>
+  </si>
+  <si>
     <t>AuteurDocument.auteur[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ProfessionnelDocument
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ProfessionnelAuteurDocument
 https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PatientDocumenthttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/SystemeDocument</t>
   </si>
   <si>
@@ -569,11 +585,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ4"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.41015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.41015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.3046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -603,7 +619,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.41015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.3046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1019,6 +1035,206 @@
         <v>72</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Professionnel ou patient/usager ou système, auteur du document incluant la structure de rattachement de l'auteur. L'auteur du document peut être un professionnel, un patient ou un système.</t>
+    <t>Auteur du document : ce peut être un professionnel, un patient/usager ou un système. Pour un professionnel ou un système, la structure de rattachement doit être précisée.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-AuteurDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
